--- a/tools/excel/cmmc/cmmc-2.0.xlsx
+++ b/tools/excel/cmmc/cmmc-2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\tarkadia\projects\intuitem\ciso-assistant-community\tools\excel\cmmc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CAF9F47-73BD-4DE8-88A8-75005AE6F9B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA53C337-614A-4F0B-A152-D7C5833C7673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="492" windowWidth="17136" windowHeight="10008" tabRatio="888" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="888" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="513">
   <si>
     <t>type</t>
   </si>
@@ -1951,6 +1951,9 @@
       <t xml:space="preserve">
 We have deliberately left an extra blank line in the "questions" column to remind us that this framework has an issue with an extra blank question appearing as the first question of requirement "SI.L2-3.14.6"! You must delete everything related to "question1" for this specific node in the final YAML file!</t>
     </r>
+  </si>
+  <si>
+    <t>6</t>
   </si>
 </sst>
 </file>
@@ -2205,41 +2208,41 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2473,13 +2476,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -2501,6 +2497,13 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2550,7 +2553,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C0055941-D680-47C7-A8BB-7A29694B95E7}" name="Tableau1" displayName="Tableau1" ref="A1:H125" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C0055941-D680-47C7-A8BB-7A29694B95E7}" name="Tableau1" displayName="Tableau1" ref="A1:H125" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <autoFilter ref="A1:H125" xr:uid="{C0055941-D680-47C7-A8BB-7A29694B95E7}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{026D1494-67DE-47F4-87E2-E8D1711AA171}" name="assessable" dataDxfId="7"/>
@@ -2878,8 +2881,8 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2">
-        <v>5</v>
+      <c r="B3" s="2" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
